--- a/data/trans_dic/P22$concerIndv-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P22$concerIndv-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menor, es beneficiaria de Seguro Médico concertado individualmente</t>
+          <t>Población que, al menos, es beneficiaria de seguro médico concertado individualmente (tasa de respuesta: 99,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,47</t>
+          <t>0,15; 1,4</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,0; 3,52</t>
+          <t>1,09; 3,46</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,78; 2,98</t>
+          <t>0,79; 2,92</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,52; 3,97</t>
+          <t>1,57; 4,08</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,49; 2,45</t>
+          <t>0,46; 2,27</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,94; 3,31</t>
+          <t>0,92; 3,16</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,82; 2,76</t>
+          <t>0,71; 2,58</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,32; 4,45</t>
+          <t>2,34; 4,46</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,45; 1,53</t>
+          <t>0,43; 1,47</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,14; 2,81</t>
+          <t>1,16; 2,85</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,99; 2,33</t>
+          <t>0,97; 2,31</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,16; 3,74</t>
+          <t>2,17; 3,88</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,97; 2,6</t>
+          <t>0,95; 2,64</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,64; 3,83</t>
+          <t>1,6; 3,6</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,01; 4,39</t>
+          <t>1,97; 4,4</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,22; 6,82</t>
+          <t>2,28; 6,95</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,89; 4,15</t>
+          <t>1,87; 4,11</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,03; 2,67</t>
+          <t>1,12; 2,72</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,38; 6,01</t>
+          <t>3,19; 5,88</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,27; 7,95</t>
+          <t>5,22; 7,89</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,68; 3,03</t>
+          <t>1,63; 3,08</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,58; 2,89</t>
+          <t>1,55; 2,86</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,93; 4,77</t>
+          <t>2,89; 4,71</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,58; 6,7</t>
+          <t>3,5; 6,68</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,93; 6,35</t>
+          <t>2,93; 6,25</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,67; 6,09</t>
+          <t>2,73; 6,05</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,62; 4,02</t>
+          <t>1,67; 4,08</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,92; 8,68</t>
+          <t>4,93; 8,89</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,82; 7,41</t>
+          <t>3,82; 7,13</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,61; 5,83</t>
+          <t>2,68; 6,16</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,46; 5,1</t>
+          <t>2,49; 5,11</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,71; 9,94</t>
+          <t>3,49; 9,68</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,66; 6,05</t>
+          <t>3,66; 6,12</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,98; 5,31</t>
+          <t>3,07; 5,41</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,31; 4,19</t>
+          <t>2,35; 4,14</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4,64; 8,48</t>
+          <t>4,75; 8,56</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,43; 6,14</t>
+          <t>3,43; 6,03</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,17; 5,96</t>
+          <t>3,1; 6,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,45; 7,41</t>
+          <t>4,3; 7,32</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7,83; 11,74</t>
+          <t>7,77; 11,82</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,45; 7,48</t>
+          <t>4,54; 7,56</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,05; 7,08</t>
+          <t>4,15; 7,04</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,58; 9,08</t>
+          <t>5,48; 8,96</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>9,69; 14,24</t>
+          <t>9,77; 14,14</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,38; 6,31</t>
+          <t>4,36; 6,45</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4,03; 6,06</t>
+          <t>3,91; 5,96</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5,32; 7,53</t>
+          <t>5,35; 7,65</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>9,39; 12,34</t>
+          <t>9,45; 12,24</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,31; 3,4</t>
+          <t>2,27; 3,43</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,66; 3,95</t>
+          <t>2,62; 3,97</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,75; 4,09</t>
+          <t>2,76; 4,03</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,66; 7,06</t>
+          <t>4,78; 7,09</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,28; 4,66</t>
+          <t>3,28; 4,7</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,71; 4,05</t>
+          <t>2,71; 4,08</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,77; 5,25</t>
+          <t>3,74; 5,18</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>6,27; 8,7</t>
+          <t>6,25; 8,7</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,9; 3,82</t>
+          <t>2,97; 3,85</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2,87; 3,74</t>
+          <t>2,87; 3,76</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3,48; 4,45</t>
+          <t>3,47; 4,43</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>5,97; 7,6</t>
+          <t>5,93; 7,67</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menor, es beneficiaria de Seguro Médico concertado individualmente</t>
+          <t>Población que, al menos, es beneficiaria de seguro médico concertado individualmente (tasa de respuesta: 99,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1124; 10176</t>
+          <t>1008; 9693</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>7007; 24781</t>
+          <t>7678; 24329</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5240; 20077</t>
+          <t>5298; 19700</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9665; 25204</t>
+          <t>9960; 25916</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>3376; 16873</t>
+          <t>3149; 15623</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6565; 23080</t>
+          <t>6411; 22020</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5503; 18538</t>
+          <t>4756; 17385</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>15658; 30053</t>
+          <t>15811; 30138</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>6250; 21075</t>
+          <t>5924; 20308</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>16032; 39346</t>
+          <t>16204; 39851</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>13335; 31404</t>
+          <t>13038; 31120</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>28285; 49035</t>
+          <t>28494; 50852</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9290; 24938</t>
+          <t>9148; 25357</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>16682; 38959</t>
+          <t>16230; 36618</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>20502; 44802</t>
+          <t>20145; 44904</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>26510; 81364</t>
+          <t>27194; 82862</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>18259; 40221</t>
+          <t>18076; 39822</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10647; 27579</t>
+          <t>11574; 28103</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>35187; 62534</t>
+          <t>33249; 61198</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>50508; 76203</t>
+          <t>50033; 75585</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>32482; 58368</t>
+          <t>31422; 59508</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>32459; 59229</t>
+          <t>31707; 58528</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>60354; 98473</t>
+          <t>59568; 97246</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>77044; 144033</t>
+          <t>75186; 143632</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>19862; 42998</t>
+          <t>19848; 42326</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>20220; 46139</t>
+          <t>20696; 45834</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>12300; 30471</t>
+          <t>12663; 30946</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>34660; 61149</t>
+          <t>34760; 62678</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>26114; 50695</t>
+          <t>26128; 48779</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>20278; 45346</t>
+          <t>20828; 47841</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>19209; 39853</t>
+          <t>19449; 39886</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>34591; 92768</t>
+          <t>32588; 90387</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>49835; 82422</t>
+          <t>49832; 83341</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>45711; 81491</t>
+          <t>47069; 82995</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>35610; 64445</t>
+          <t>36192; 63770</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>76068; 138946</t>
+          <t>77760; 140150</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>32210; 57688</t>
+          <t>32272; 56640</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>30021; 56482</t>
+          <t>29375; 56878</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>41649; 69438</t>
+          <t>40319; 68601</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>72560; 108771</t>
+          <t>72056; 109576</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>46176; 77610</t>
+          <t>47141; 78391</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>42604; 74507</t>
+          <t>43653; 74083</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>58210; 94728</t>
+          <t>57233; 93506</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>105872; 155520</t>
+          <t>106684; 154522</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>86691; 124858</t>
+          <t>86140; 127583</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>80489; 121169</t>
+          <t>78215; 119192</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>105360; 149199</t>
+          <t>106025; 151536</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>189662; 249197</t>
+          <t>190774; 247231</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>75537; 111272</t>
+          <t>74314; 112315</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>91137; 135348</t>
+          <t>89588; 135994</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>93270; 138724</t>
+          <t>93646; 136753</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>161243; 244335</t>
+          <t>165539; 245205</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>110874; 157521</t>
+          <t>110901; 158730</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>96570; 144198</t>
+          <t>96514; 145060</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>133323; 185772</t>
+          <t>132445; 183409</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>229379; 318533</t>
+          <t>228905; 318257</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>193013; 253601</t>
+          <t>197272; 256187</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>200265; 261234</t>
+          <t>200489; 262950</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>241127; 308326</t>
+          <t>240378; 306778</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>425087; 540954</t>
+          <t>422439; 546280</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P22$concerIndv-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P22$concerIndv-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>3,08%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,4</t>
+          <t>0,14; 1,33</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,09; 3,46</t>
+          <t>1,1; 3,47</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,79; 2,92</t>
+          <t>0,8; 2,99</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,57; 4,08</t>
+          <t>1,71; 4,29</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,46; 2,27</t>
+          <t>0,45; 2,32</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,92; 3,16</t>
+          <t>0,84; 3,26</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,71; 2,58</t>
+          <t>0,77; 2,66</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,34; 4,46</t>
+          <t>2,32; 4,6</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,43; 1,47</t>
+          <t>0,45; 1,63</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,16; 2,85</t>
+          <t>1,25; 2,83</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,97; 2,31</t>
+          <t>0,89; 2,35</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,17; 3,88</t>
+          <t>2,33; 4,0</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>6,14%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,95; 2,64</t>
+          <t>0,88; 2,58</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,6; 3,6</t>
+          <t>1,58; 3,66</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,97; 4,4</t>
+          <t>1,99; 4,42</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,28; 6,95</t>
+          <t>4,12; 7,76</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,87; 4,11</t>
+          <t>1,88; 4,11</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,12; 2,72</t>
+          <t>1,1; 2,69</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,19; 5,88</t>
+          <t>3,29; 5,96</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,22; 7,89</t>
+          <t>5,39; 8,09</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,63; 3,08</t>
+          <t>1,63; 3,03</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,55; 2,86</t>
+          <t>1,5; 2,83</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,89; 4,71</t>
+          <t>2,93; 4,75</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,5; 6,68</t>
+          <t>5,17; 7,43</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>8,4%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,93; 6,25</t>
+          <t>2,87; 6,41</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,73; 6,05</t>
+          <t>2,69; 5,99</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,67; 4,08</t>
+          <t>1,7; 4,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,93; 8,89</t>
+          <t>5,53; 9,48</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,82; 7,13</t>
+          <t>3,94; 7,53</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,68; 6,16</t>
+          <t>2,68; 5,85</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,49; 5,11</t>
+          <t>2,4; 5,09</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,49; 9,68</t>
+          <t>7,72; 11,92</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,66; 6,12</t>
+          <t>3,66; 6,1</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3,07; 5,41</t>
+          <t>2,86; 5,22</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,35; 4,14</t>
+          <t>2,33; 4,05</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4,75; 8,56</t>
+          <t>6,97; 9,76</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>11,25%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,43; 6,03</t>
+          <t>3,49; 6,04</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,1; 6,0</t>
+          <t>3,16; 6,06</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,3; 7,32</t>
+          <t>4,27; 7,28</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7,77; 11,82</t>
+          <t>7,88; 11,79</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,54; 7,56</t>
+          <t>4,33; 7,43</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,15; 7,04</t>
+          <t>4,17; 6,98</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,48; 8,96</t>
+          <t>5,44; 8,84</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>9,77; 14,14</t>
+          <t>11,01; 14,64</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,36; 6,45</t>
+          <t>4,46; 6,42</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3,91; 5,96</t>
+          <t>4,07; 6,04</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5,35; 7,65</t>
+          <t>5,29; 7,57</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>9,45; 12,24</t>
+          <t>10,15; 12,84</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>7,53%</t>
         </is>
       </c>
     </row>
@@ -1277,42 +1277,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,27; 3,43</t>
+          <t>2,29; 3,4</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,62; 3,97</t>
+          <t>2,64; 3,93</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,76; 4,03</t>
+          <t>2,78; 3,99</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,78; 7,09</t>
+          <t>5,74; 7,57</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,28; 4,7</t>
+          <t>3,3; 4,62</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,71; 4,08</t>
+          <t>2,76; 4,01</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,74; 5,18</t>
+          <t>3,68; 5,16</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>6,25; 8,7</t>
+          <t>7,65; 9,25</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1322,17 +1322,17 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2,87; 3,76</t>
+          <t>2,89; 3,81</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3,47; 4,43</t>
+          <t>3,51; 4,45</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>5,93; 7,67</t>
+          <t>6,99; 8,1</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16050</t>
+          <t>19161</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>21893</t>
+          <t>24756</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>37943</t>
+          <t>43918</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1008; 9693</t>
+          <t>953; 9176</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>7678; 24329</t>
+          <t>7758; 24410</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5298; 19700</t>
+          <t>5415; 20161</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9960; 25916</t>
+          <t>11814; 29600</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>3149; 15623</t>
+          <t>3091; 15956</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6411; 22020</t>
+          <t>5842; 22692</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4756; 17385</t>
+          <t>5169; 17876</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>15811; 30138</t>
+          <t>17020; 33751</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>5924; 20308</t>
+          <t>6245; 22462</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>16204; 39851</t>
+          <t>17519; 39580</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>13038; 31120</t>
+          <t>12004; 31654</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>28494; 50852</t>
+          <t>33243; 56904</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>54853</t>
+          <t>59947</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>61797</t>
+          <t>70205</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>116651</t>
+          <t>130152</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9148; 25357</t>
+          <t>8414; 24758</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>16230; 36618</t>
+          <t>16052; 37265</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>20145; 44904</t>
+          <t>20299; 45160</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>27194; 82862</t>
+          <t>43184; 81345</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>18076; 39822</t>
+          <t>18239; 39831</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11574; 28103</t>
+          <t>11340; 27727</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>33249; 61198</t>
+          <t>34211; 62065</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>50033; 75585</t>
+          <t>57726; 86641</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>31422; 59508</t>
+          <t>31394; 58370</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>31707; 58528</t>
+          <t>30665; 58018</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>59568; 97246</t>
+          <t>60484; 97961</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>75186; 143632</t>
+          <t>109603; 157572</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>48154</t>
+          <t>57862</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>65913</t>
+          <t>77868</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>114066</t>
+          <t>135729</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>19848; 42326</t>
+          <t>19462; 43408</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>20696; 45834</t>
+          <t>20394; 45378</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>12663; 30946</t>
+          <t>12908; 30281</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>34760; 62678</t>
+          <t>44374; 76092</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>26128; 48779</t>
+          <t>26923; 51476</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>20828; 47841</t>
+          <t>20815; 45426</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>19449; 39886</t>
+          <t>18758; 39775</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>32588; 90387</t>
+          <t>62744; 96812</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>49832; 83341</t>
+          <t>49784; 83074</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>47069; 82995</t>
+          <t>43846; 80051</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>36192; 63770</t>
+          <t>35831; 62383</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>77760; 140150</t>
+          <t>112510; 157708</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>88301</t>
+          <t>95176</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>132593</t>
+          <t>141941</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>220894</t>
+          <t>237117</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>32272; 56640</t>
+          <t>32837; 56748</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>29375; 56878</t>
+          <t>29963; 57402</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>40319; 68601</t>
+          <t>40038; 68223</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>72056; 109576</t>
+          <t>78026; 116764</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>47141; 78391</t>
+          <t>44934; 77054</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>43653; 74083</t>
+          <t>43831; 73429</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>57233; 93506</t>
+          <t>56834; 92219</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>106684; 154522</t>
+          <t>122972; 163584</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>86140; 127583</t>
+          <t>88151; 126919</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>78215; 119192</t>
+          <t>81457; 120683</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>106025; 151536</t>
+          <t>104793; 149903</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>190774; 247231</t>
+          <t>213826; 270515</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>207358</t>
+          <t>232146</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>282196</t>
+          <t>314769</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>489554</t>
+          <t>546915</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>74314; 112315</t>
+          <t>74994; 111322</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>89588; 135994</t>
+          <t>90345; 134649</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>93646; 136753</t>
+          <t>94356; 135245</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>165539; 245205</t>
+          <t>202795; 267343</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>110901; 158730</t>
+          <t>111302; 156032</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>96514; 145060</t>
+          <t>98099; 142696</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>132445; 183409</t>
+          <t>130180; 182601</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>228905; 318257</t>
+          <t>285695; 345363</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>197272; 256187</t>
+          <t>197741; 255619</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>200489; 262950</t>
+          <t>202108; 266053</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>240378; 306778</t>
+          <t>243048; 308286</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>422439; 546280</t>
+          <t>507717; 588258</t>
         </is>
       </c>
     </row>
